--- a/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
+++ b/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
@@ -7,14 +7,15 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Parametros_Posteriores" sheetId="1" r:id="rId1"/>
+    <sheet name="Diagnosticos_Convergencia" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>mean</t>
   </si>
@@ -46,13 +47,43 @@
     <t>alpha</t>
   </si>
   <si>
-    <t>sigma_phi</t>
+    <t>beta_area</t>
+  </si>
+  <si>
+    <t>sigma_s</t>
+  </si>
+  <si>
+    <t>rho</t>
   </si>
   <si>
     <t>sigma_t</t>
   </si>
   <si>
     <t>alpha_disp</t>
+  </si>
+  <si>
+    <t>Diagnóstico</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Total Cadenas</t>
+  </si>
+  <si>
+    <t>Muestras por Cadena (Draws)</t>
+  </si>
+  <si>
+    <t>Divergencias NUTS</t>
+  </si>
+  <si>
+    <t>R_hat Máximo</t>
+  </si>
+  <si>
+    <t>ESS Bulk Mínimo</t>
+  </si>
+  <si>
+    <t>ESS Tail Mínimo</t>
   </si>
 </sst>
 </file>
@@ -410,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -447,28 +478,31 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>1.4564</v>
+        <v>1.525</v>
       </c>
       <c r="C2">
-        <v>0.3035</v>
+        <v>0.0566</v>
       </c>
       <c r="D2">
-        <v>0.9409999999999999</v>
+        <v>1.4225</v>
       </c>
       <c r="E2">
-        <v>2.0677</v>
+        <v>1.6373</v>
       </c>
       <c r="F2">
-        <v>0.0134</v>
+        <v>0.0009</v>
       </c>
       <c r="G2">
-        <v>0.008399999999999999</v>
+        <v>0.0011</v>
       </c>
       <c r="H2">
-        <v>517.4503999999999</v>
+        <v>4161.7755</v>
       </c>
       <c r="I2">
-        <v>575.4913</v>
+        <v>2574.1111</v>
+      </c>
+      <c r="J2">
+        <v>1.004</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -476,28 +510,31 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>1.6372</v>
+        <v>0.2283</v>
       </c>
       <c r="C3">
-        <v>0.3188</v>
+        <v>0.0721</v>
       </c>
       <c r="D3">
-        <v>1.0495</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="E3">
-        <v>2.2162</v>
+        <v>0.3642</v>
       </c>
       <c r="F3">
-        <v>0.0137</v>
+        <v>0.0023</v>
       </c>
       <c r="G3">
-        <v>0.0095</v>
+        <v>0.0011</v>
       </c>
       <c r="H3">
-        <v>563.2382</v>
+        <v>1035.6203</v>
       </c>
       <c r="I3">
-        <v>536.9725</v>
+        <v>1627.4953</v>
+      </c>
+      <c r="J3">
+        <v>1.004</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -505,28 +542,31 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>1.1306</v>
+        <v>1.4981</v>
       </c>
       <c r="C4">
-        <v>0.2967</v>
+        <v>0.1467</v>
       </c>
       <c r="D4">
-        <v>0.6706</v>
+        <v>1.251</v>
       </c>
       <c r="E4">
-        <v>1.7284</v>
+        <v>1.7835</v>
       </c>
       <c r="F4">
-        <v>0.0116</v>
+        <v>0.0066</v>
       </c>
       <c r="G4">
-        <v>0.009299999999999999</v>
+        <v>0.0028</v>
       </c>
       <c r="H4">
-        <v>665.0709000000001</v>
+        <v>505.265</v>
       </c>
       <c r="I4">
-        <v>575.4913</v>
+        <v>1180.2868</v>
+      </c>
+      <c r="J4">
+        <v>1.011</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -534,28 +574,161 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>0.4919</v>
+        <v>0.8172</v>
       </c>
       <c r="C5">
-        <v>0.1166</v>
+        <v>0.0979</v>
       </c>
       <c r="D5">
-        <v>0.2964</v>
+        <v>0.6522</v>
       </c>
       <c r="E5">
-        <v>0.7085</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0.0048</v>
+        <v>0.005</v>
       </c>
       <c r="G5">
-        <v>0.0038</v>
+        <v>0.0026</v>
       </c>
       <c r="H5">
-        <v>559.6241</v>
+        <v>336.224</v>
       </c>
       <c r="I5">
-        <v>482.985</v>
+        <v>352.6789</v>
+      </c>
+      <c r="J5">
+        <v>1.0175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>0.6082</v>
+      </c>
+      <c r="C6">
+        <v>0.5517</v>
+      </c>
+      <c r="D6">
+        <v>0.0687</v>
+      </c>
+      <c r="E6">
+        <v>1.664</v>
+      </c>
+      <c r="F6">
+        <v>0.0098</v>
+      </c>
+      <c r="G6">
+        <v>0.0133</v>
+      </c>
+      <c r="H6">
+        <v>2740.2197</v>
+      </c>
+      <c r="I6">
+        <v>2576.6951</v>
+      </c>
+      <c r="J6">
+        <v>1.0004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>5.3376</v>
+      </c>
+      <c r="C7">
+        <v>0.9151</v>
+      </c>
+      <c r="D7">
+        <v>3.7416</v>
+      </c>
+      <c r="E7">
+        <v>7.1407</v>
+      </c>
+      <c r="F7">
+        <v>0.0226</v>
+      </c>
+      <c r="G7">
+        <v>0.0147</v>
+      </c>
+      <c r="H7">
+        <v>1584.7369</v>
+      </c>
+      <c r="I7">
+        <v>2129.6279</v>
+      </c>
+      <c r="J7">
+        <v>1.001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>1.0175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
+        <v>336.224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <v>352.6789</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
+++ b/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
@@ -9,13 +9,15 @@
   <sheets>
     <sheet name="Parametros_Posteriores" sheetId="1" r:id="rId1"/>
     <sheet name="Diagnosticos_Convergencia" sheetId="2" r:id="rId2"/>
+    <sheet name="Validacion_ADVI_vs_NUTS" sheetId="3" r:id="rId3"/>
+    <sheet name="Estabilidad_Semillas" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>mean</t>
   </si>
@@ -47,6 +49,9 @@
     <t>alpha</t>
   </si>
   <si>
+    <t>beta_year</t>
+  </si>
+  <si>
     <t>beta_area</t>
   </si>
   <si>
@@ -56,9 +61,6 @@
     <t>rho</t>
   </si>
   <si>
-    <t>sigma_t</t>
-  </si>
-  <si>
     <t>alpha_disp</t>
   </si>
   <si>
@@ -68,22 +70,238 @@
     <t>Valor</t>
   </si>
   <si>
-    <t>Total Cadenas</t>
-  </si>
-  <si>
-    <t>Muestras por Cadena (Draws)</t>
-  </si>
-  <si>
-    <t>Divergencias NUTS</t>
-  </si>
-  <si>
-    <t>R_hat Máximo</t>
-  </si>
-  <si>
-    <t>ESS Bulk Mínimo</t>
-  </si>
-  <si>
-    <t>ESS Tail Mínimo</t>
+    <t>Método de Inferencia</t>
+  </si>
+  <si>
+    <t>Muestras Posteriores Extraídas</t>
+  </si>
+  <si>
+    <t>Criterio de Convergencia</t>
+  </si>
+  <si>
+    <t>ELPD_WAIC</t>
+  </si>
+  <si>
+    <t>ELPD_WAIC_SE</t>
+  </si>
+  <si>
+    <t>p_WAIC</t>
+  </si>
+  <si>
+    <t>ELPD_LOO</t>
+  </si>
+  <si>
+    <t>ELPD_LOO_SE</t>
+  </si>
+  <si>
+    <t>p_LOO</t>
+  </si>
+  <si>
+    <t>Pareto-k &lt; 0.5 (Observaciones)</t>
+  </si>
+  <si>
+    <t>Pareto-k [0.5, 0.7] (Observaciones)</t>
+  </si>
+  <si>
+    <t>Pareto-k &gt; 0.7 (Observaciones)</t>
+  </si>
+  <si>
+    <t>Advertencia Pareto-k</t>
+  </si>
+  <si>
+    <t>Rho Media Posterior</t>
+  </si>
+  <si>
+    <t>Rho HDI 95% Inferior</t>
+  </si>
+  <si>
+    <t>Rho HDI 95% Superior</t>
+  </si>
+  <si>
+    <t>Beta_Year Media Posterior</t>
+  </si>
+  <si>
+    <t>Beta_Year HDI 95% Inferior</t>
+  </si>
+  <si>
+    <t>Beta_Year HDI 95% Superior</t>
+  </si>
+  <si>
+    <t>ADVI (Automatic Differentiation Variational Inference)</t>
+  </si>
+  <si>
+    <t>CheckParametersConvergence (tolerancia 1e-4)</t>
+  </si>
+  <si>
+    <t>Advertencia: observaciones con k&gt;0.7 presentes</t>
+  </si>
+  <si>
+    <t>Parámetro</t>
+  </si>
+  <si>
+    <t>Media_ADVI</t>
+  </si>
+  <si>
+    <t>SD_ADVI</t>
+  </si>
+  <si>
+    <t>HDI_95_ADVI</t>
+  </si>
+  <si>
+    <t>Media_NUTS</t>
+  </si>
+  <si>
+    <t>SD_NUTS</t>
+  </si>
+  <si>
+    <t>HDI_95_NUTS</t>
+  </si>
+  <si>
+    <t>Ratio_SD (ADVI/NUTS)</t>
+  </si>
+  <si>
+    <t>Subestimacion_Incertidumbre_Pct</t>
+  </si>
+  <si>
+    <t>Intercepto Cantonal (alpha)</t>
+  </si>
+  <si>
+    <t>Contraste Anual 2025 vs 2024 (beta_year)</t>
+  </si>
+  <si>
+    <t>Elasticidad Área Territorial (beta_area)</t>
+  </si>
+  <si>
+    <t>Escala Espacial BYM2 (sigma_s)</t>
+  </si>
+  <si>
+    <t>Parámetro de Mezcla Espacial (rho)</t>
+  </si>
+  <si>
+    <t>Dispersión Binomial Negativa (alpha_disp)</t>
+  </si>
+  <si>
+    <t>[1.5327, 1.7101]</t>
+  </si>
+  <si>
+    <t>[0.1995, 0.4422]</t>
+  </si>
+  <si>
+    <t>[0.0510, 0.1734]</t>
+  </si>
+  <si>
+    <t>[0.8449, 1.0320]</t>
+  </si>
+  <si>
+    <t>[0.0009, 0.1485]</t>
+  </si>
+  <si>
+    <t>[1.5588, 2.3266]</t>
+  </si>
+  <si>
+    <t>[1.2374, 1.4995]</t>
+  </si>
+  <si>
+    <t>[0.1903, 0.4278]</t>
+  </si>
+  <si>
+    <t>[0.0939, 0.3820]</t>
+  </si>
+  <si>
+    <t>[1.2423, 1.8463]</t>
+  </si>
+  <si>
+    <t>[0.5891, 0.9892]</t>
+  </si>
+  <si>
+    <t>[3.8136, 7.3525]</t>
+  </si>
+  <si>
+    <t>+32.6%</t>
+  </si>
+  <si>
+    <t>-1.7%</t>
+  </si>
+  <si>
+    <t>+57.8%</t>
+  </si>
+  <si>
+    <t>+69.7%</t>
+  </si>
+  <si>
+    <t>+59.2%</t>
+  </si>
+  <si>
+    <t>+79.0%</t>
+  </si>
+  <si>
+    <t>Semilla</t>
+  </si>
+  <si>
+    <t>ELBO_Final</t>
+  </si>
+  <si>
+    <t>ELBO_Meseta_Media</t>
+  </si>
+  <si>
+    <t>Iteraciones</t>
+  </si>
+  <si>
+    <t>Convergio</t>
+  </si>
+  <si>
+    <t>alpha_media</t>
+  </si>
+  <si>
+    <t>alpha_sd</t>
+  </si>
+  <si>
+    <t>beta_year_media</t>
+  </si>
+  <si>
+    <t>beta_year_sd</t>
+  </si>
+  <si>
+    <t>beta_area_media</t>
+  </si>
+  <si>
+    <t>beta_area_sd</t>
+  </si>
+  <si>
+    <t>sigma_s_media</t>
+  </si>
+  <si>
+    <t>sigma_s_sd</t>
+  </si>
+  <si>
+    <t>rho_media</t>
+  </si>
+  <si>
+    <t>rho_sd</t>
+  </si>
+  <si>
+    <t>rho_hdi_inf</t>
+  </si>
+  <si>
+    <t>rho_hdi_sup</t>
+  </si>
+  <si>
+    <t>alpha_disp_media</t>
+  </si>
+  <si>
+    <t>alpha_disp_sd</t>
+  </si>
+  <si>
+    <t>Media (Entre Semillas)</t>
+  </si>
+  <si>
+    <t>Desv. Est. (Entre Semillas)</t>
+  </si>
+  <si>
+    <t>Sí (100%)</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -478,31 +696,28 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>1.525</v>
+        <v>1.6235</v>
       </c>
       <c r="C2">
-        <v>0.0566</v>
+        <v>0.0449</v>
       </c>
       <c r="D2">
-        <v>1.4225</v>
+        <v>1.54</v>
       </c>
       <c r="E2">
-        <v>1.6373</v>
+        <v>1.7101</v>
       </c>
       <c r="F2">
-        <v>0.0009</v>
+        <v>0.001</v>
       </c>
       <c r="G2">
-        <v>0.0011</v>
+        <v>0.0007</v>
       </c>
       <c r="H2">
-        <v>4161.7755</v>
+        <v>1919.8995</v>
       </c>
       <c r="I2">
-        <v>2574.1111</v>
-      </c>
-      <c r="J2">
-        <v>1.004</v>
+        <v>1779.1585</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -510,31 +725,28 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.2283</v>
+        <v>0.3175</v>
       </c>
       <c r="C3">
-        <v>0.0721</v>
+        <v>0.0613</v>
       </c>
       <c r="D3">
-        <v>0.09279999999999999</v>
+        <v>0.2047</v>
       </c>
       <c r="E3">
-        <v>0.3642</v>
+        <v>0.4369</v>
       </c>
       <c r="F3">
-        <v>0.0023</v>
+        <v>0.0013</v>
       </c>
       <c r="G3">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="H3">
-        <v>1035.6203</v>
+        <v>2114.2896</v>
       </c>
       <c r="I3">
-        <v>1627.4953</v>
-      </c>
-      <c r="J3">
-        <v>1.004</v>
+        <v>1782.2167</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -542,31 +754,28 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>1.4981</v>
+        <v>0.114</v>
       </c>
       <c r="C4">
-        <v>0.1467</v>
+        <v>0.0316</v>
       </c>
       <c r="D4">
-        <v>1.251</v>
+        <v>0.0541</v>
       </c>
       <c r="E4">
-        <v>1.7835</v>
+        <v>0.1725</v>
       </c>
       <c r="F4">
-        <v>0.0066</v>
+        <v>0.0007</v>
       </c>
       <c r="G4">
-        <v>0.0028</v>
+        <v>0.0005</v>
       </c>
       <c r="H4">
-        <v>505.265</v>
+        <v>1893.0735</v>
       </c>
       <c r="I4">
-        <v>1180.2868</v>
-      </c>
-      <c r="J4">
-        <v>1.011</v>
+        <v>1920.3398</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -574,31 +783,28 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>0.8172</v>
+        <v>0.9327</v>
       </c>
       <c r="C5">
-        <v>0.0979</v>
+        <v>0.047</v>
       </c>
       <c r="D5">
-        <v>0.6522</v>
+        <v>0.848</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>1.0252</v>
       </c>
       <c r="F5">
-        <v>0.005</v>
+        <v>0.0011</v>
       </c>
       <c r="G5">
-        <v>0.0026</v>
+        <v>0.0008</v>
       </c>
       <c r="H5">
-        <v>336.224</v>
+        <v>1926.7957</v>
       </c>
       <c r="I5">
-        <v>352.6789</v>
-      </c>
-      <c r="J5">
-        <v>1.0175</v>
+        <v>1744.0399</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -606,31 +812,28 @@
         <v>13</v>
       </c>
       <c r="B6">
-        <v>0.6082</v>
+        <v>0.0274</v>
       </c>
       <c r="C6">
-        <v>0.5517</v>
+        <v>0.0429</v>
       </c>
       <c r="D6">
-        <v>0.0687</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1.664</v>
+        <v>0.0906</v>
       </c>
       <c r="F6">
-        <v>0.0098</v>
+        <v>0.001</v>
       </c>
       <c r="G6">
-        <v>0.0133</v>
+        <v>0.0024</v>
       </c>
       <c r="H6">
-        <v>2740.2197</v>
+        <v>1986.8933</v>
       </c>
       <c r="I6">
-        <v>2576.6951</v>
-      </c>
-      <c r="J6">
-        <v>1.0004</v>
+        <v>1921.861</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -638,31 +841,28 @@
         <v>14</v>
       </c>
       <c r="B7">
-        <v>5.3376</v>
+        <v>1.8953</v>
       </c>
       <c r="C7">
-        <v>0.9151</v>
+        <v>0.1903</v>
       </c>
       <c r="D7">
-        <v>3.7416</v>
+        <v>1.5532</v>
       </c>
       <c r="E7">
-        <v>7.1407</v>
+        <v>2.2696</v>
       </c>
       <c r="F7">
-        <v>0.0226</v>
+        <v>0.0044</v>
       </c>
       <c r="G7">
-        <v>0.0147</v>
+        <v>0.003</v>
       </c>
       <c r="H7">
-        <v>1584.7369</v>
+        <v>1862.6901</v>
       </c>
       <c r="I7">
-        <v>2129.6279</v>
-      </c>
-      <c r="J7">
-        <v>1.001</v>
+        <v>1882.1067</v>
       </c>
     </row>
   </sheetData>
@@ -672,7 +872,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -687,8 +887,8 @@
       <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2">
-        <v>4</v>
+      <c r="B2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -696,15 +896,15 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>19</v>
       </c>
-      <c r="B4">
-        <v>22</v>
+      <c r="B4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -712,7 +912,7 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>1.0175</v>
+        <v>-1473.724258527367</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -720,7 +920,7 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>336.224</v>
+        <v>26.17493962971699</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -728,7 +928,688 @@
         <v>22</v>
       </c>
       <c r="B7">
-        <v>352.6789</v>
+        <v>167.9849583339543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8">
+        <v>-1537.056294417802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9">
+        <v>30.86485530288633</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>231.316994224389</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>0.02743806563775158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16">
+        <v>0.0009044670208433613</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17">
+        <v>0.1484819000085819</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18">
+        <v>0.3174807836015135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19">
+        <v>0.199521462273394</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20">
+        <v>0.4421612885874928</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2">
+        <v>1.6235</v>
+      </c>
+      <c r="C2">
+        <v>0.0449</v>
+      </c>
+      <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2">
+        <v>1.3701</v>
+      </c>
+      <c r="F2">
+        <v>0.0667</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2">
+        <v>0.6737</v>
+      </c>
+      <c r="I2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3">
+        <v>0.3175</v>
+      </c>
+      <c r="C3">
+        <v>0.0613</v>
+      </c>
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3">
+        <v>0.3093</v>
+      </c>
+      <c r="F3">
+        <v>0.0603</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3">
+        <v>1.0172</v>
+      </c>
+      <c r="I3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4">
+        <v>0.114</v>
+      </c>
+      <c r="C4">
+        <v>0.0316</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4">
+        <v>0.2306</v>
+      </c>
+      <c r="F4">
+        <v>0.075</v>
+      </c>
+      <c r="G4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4">
+        <v>0.422</v>
+      </c>
+      <c r="I4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5">
+        <v>0.9327</v>
+      </c>
+      <c r="C5">
+        <v>0.047</v>
+      </c>
+      <c r="D5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5">
+        <v>1.4986</v>
+      </c>
+      <c r="F5">
+        <v>0.1553</v>
+      </c>
+      <c r="G5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5">
+        <v>0.3025</v>
+      </c>
+      <c r="I5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6">
+        <v>0.0274</v>
+      </c>
+      <c r="C6">
+        <v>0.0429</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6">
+        <v>0.8127</v>
+      </c>
+      <c r="F6">
+        <v>0.1052</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6">
+        <v>0.4078</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7">
+        <v>1.8953</v>
+      </c>
+      <c r="C7">
+        <v>0.1903</v>
+      </c>
+      <c r="D7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7">
+        <v>5.3588</v>
+      </c>
+      <c r="F7">
+        <v>0.9064</v>
+      </c>
+      <c r="G7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7">
+        <v>0.2099</v>
+      </c>
+      <c r="I7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2">
+        <v>42</v>
+      </c>
+      <c r="B2">
+        <v>-3359.57</v>
+      </c>
+      <c r="C2">
+        <v>-1802.64</v>
+      </c>
+      <c r="D2">
+        <v>40000</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1.623524116197549</v>
+      </c>
+      <c r="G2">
+        <v>0.04491802682084656</v>
+      </c>
+      <c r="H2">
+        <v>0.3174807836015135</v>
+      </c>
+      <c r="I2">
+        <v>0.06132663748723281</v>
+      </c>
+      <c r="J2">
+        <v>0.1139655428802458</v>
+      </c>
+      <c r="K2">
+        <v>0.03163176786816241</v>
+      </c>
+      <c r="L2">
+        <v>0.9326691078819246</v>
+      </c>
+      <c r="M2">
+        <v>0.04699295345166132</v>
+      </c>
+      <c r="N2">
+        <v>0.02743806563775158</v>
+      </c>
+      <c r="O2">
+        <v>0.04290666347412147</v>
+      </c>
+      <c r="P2">
+        <v>0.0009044670208433613</v>
+      </c>
+      <c r="Q2">
+        <v>0.1484819000085819</v>
+      </c>
+      <c r="R2">
+        <v>1.895346243636717</v>
+      </c>
+      <c r="S2">
+        <v>0.1902601476808199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3">
+        <v>123</v>
+      </c>
+      <c r="B3">
+        <v>-2487.22</v>
+      </c>
+      <c r="C3">
+        <v>-1770.63</v>
+      </c>
+      <c r="D3">
+        <v>40000</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1.623778128408778</v>
+      </c>
+      <c r="G3">
+        <v>0.04584008542277374</v>
+      </c>
+      <c r="H3">
+        <v>0.3157588275025591</v>
+      </c>
+      <c r="I3">
+        <v>0.06362749840830575</v>
+      </c>
+      <c r="J3">
+        <v>0.1174209625611862</v>
+      </c>
+      <c r="K3">
+        <v>0.03042671778153327</v>
+      </c>
+      <c r="L3">
+        <v>0.9409101874383361</v>
+      </c>
+      <c r="M3">
+        <v>0.046780919908641</v>
+      </c>
+      <c r="N3">
+        <v>0.02709636327193479</v>
+      </c>
+      <c r="O3">
+        <v>0.04744799163816882</v>
+      </c>
+      <c r="P3">
+        <v>0.0009279205806517582</v>
+      </c>
+      <c r="Q3">
+        <v>0.145583162857086</v>
+      </c>
+      <c r="R3">
+        <v>1.885934853597718</v>
+      </c>
+      <c r="S3">
+        <v>0.1876216406785289</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4">
+        <v>999</v>
+      </c>
+      <c r="B4">
+        <v>-1643.06</v>
+      </c>
+      <c r="C4">
+        <v>-1816.74</v>
+      </c>
+      <c r="D4">
+        <v>40000</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1.628772147178876</v>
+      </c>
+      <c r="G4">
+        <v>0.04522113317609407</v>
+      </c>
+      <c r="H4">
+        <v>0.315314504040495</v>
+      </c>
+      <c r="I4">
+        <v>0.05965156012589985</v>
+      </c>
+      <c r="J4">
+        <v>0.1161786593041603</v>
+      </c>
+      <c r="K4">
+        <v>0.03122912729683145</v>
+      </c>
+      <c r="L4">
+        <v>0.9323345727414417</v>
+      </c>
+      <c r="M4">
+        <v>0.04684206540636381</v>
+      </c>
+      <c r="N4">
+        <v>0.02661597530497388</v>
+      </c>
+      <c r="O4">
+        <v>0.04251419240636662</v>
+      </c>
+      <c r="P4">
+        <v>0.0008799909937939831</v>
+      </c>
+      <c r="Q4">
+        <v>0.1497816357182009</v>
+      </c>
+      <c r="R4">
+        <v>1.862355073398196</v>
+      </c>
+      <c r="S4">
+        <v>0.1884001193438192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5">
+        <v>-2496.6167</v>
+      </c>
+      <c r="C5">
+        <v>-1796.67</v>
+      </c>
+      <c r="D5">
+        <v>40000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5">
+        <v>1.6254</v>
+      </c>
+      <c r="G5">
+        <v>0.0453</v>
+      </c>
+      <c r="H5">
+        <v>0.3162</v>
+      </c>
+      <c r="I5">
+        <v>0.0615</v>
+      </c>
+      <c r="J5">
+        <v>0.1159</v>
+      </c>
+      <c r="K5">
+        <v>0.0311</v>
+      </c>
+      <c r="L5">
+        <v>0.9353</v>
+      </c>
+      <c r="M5">
+        <v>0.0469</v>
+      </c>
+      <c r="N5">
+        <v>0.0271</v>
+      </c>
+      <c r="O5">
+        <v>0.0443</v>
+      </c>
+      <c r="P5">
+        <v>0.0009</v>
+      </c>
+      <c r="Q5">
+        <v>0.1479</v>
+      </c>
+      <c r="R5">
+        <v>1.8812</v>
+      </c>
+      <c r="S5">
+        <v>0.1888</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6">
+        <v>858.2936</v>
+      </c>
+      <c r="C6">
+        <v>23.6276</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6">
+        <v>0.003</v>
+      </c>
+      <c r="G6">
+        <v>0.0005</v>
+      </c>
+      <c r="H6">
+        <v>0.0011</v>
+      </c>
+      <c r="I6">
+        <v>0.002</v>
+      </c>
+      <c r="J6">
+        <v>0.0018</v>
+      </c>
+      <c r="K6">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="L6">
+        <v>0.0049</v>
+      </c>
+      <c r="M6">
+        <v>0.0001</v>
+      </c>
+      <c r="N6">
+        <v>0.0004</v>
+      </c>
+      <c r="O6">
+        <v>0.0027</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0.0021</v>
+      </c>
+      <c r="R6">
+        <v>0.017</v>
+      </c>
+      <c r="S6">
+        <v>0.0014</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
+++ b/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
@@ -10,14 +10,15 @@
     <sheet name="Parametros_Posteriores" sheetId="1" r:id="rId1"/>
     <sheet name="Diagnosticos_Convergencia" sheetId="2" r:id="rId2"/>
     <sheet name="Validacion_ADVI_vs_NUTS" sheetId="3" r:id="rId3"/>
-    <sheet name="Estabilidad_Semillas" sheetId="4" r:id="rId4"/>
+    <sheet name="Correlacion_RR_ADVI_vs_NUTS" sheetId="4" r:id="rId4"/>
+    <sheet name="Estabilidad_Semillas" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="124">
   <si>
     <t>mean</t>
   </si>
@@ -55,10 +56,7 @@
     <t>beta_area</t>
   </si>
   <si>
-    <t>sigma_s</t>
-  </si>
-  <si>
-    <t>rho</t>
+    <t>sigma_phi</t>
   </si>
   <si>
     <t>alpha_disp</t>
@@ -70,6 +68,9 @@
     <t>Valor</t>
   </si>
   <si>
+    <t>Modelo Evaluado</t>
+  </si>
+  <si>
     <t>Método de Inferencia</t>
   </si>
   <si>
@@ -109,15 +110,6 @@
     <t>Advertencia Pareto-k</t>
   </si>
   <si>
-    <t>Rho Media Posterior</t>
-  </si>
-  <si>
-    <t>Rho HDI 95% Inferior</t>
-  </si>
-  <si>
-    <t>Rho HDI 95% Superior</t>
-  </si>
-  <si>
     <t>Beta_Year Media Posterior</t>
   </si>
   <si>
@@ -127,15 +119,21 @@
     <t>Beta_Year HDI 95% Superior</t>
   </si>
   <si>
-    <t>ADVI (Automatic Differentiation Variational Inference)</t>
-  </si>
-  <si>
-    <t>CheckParametersConvergence (tolerancia 1e-4)</t>
+    <t>Modelo (c) Binomial Negativa (ICAR + No Estructurado) [Mejor LOO-CV]</t>
+  </si>
+  <si>
+    <t>ADVI (Automatic Differentiation Variational Inference, Adam lr=0.005)</t>
+  </si>
+  <si>
+    <t>Variación media móvil ELBO últimas 5,000 iteraciones &lt; 0.1%</t>
   </si>
   <si>
     <t>Advertencia: observaciones con k&gt;0.7 presentes</t>
   </si>
   <si>
+    <t>Modelo</t>
+  </si>
+  <si>
     <t>Parámetro</t>
   </si>
   <si>
@@ -157,12 +155,24 @@
     <t>HDI_95_NUTS</t>
   </si>
   <si>
+    <t>Diferencia_Relativa_Medias_Pct</t>
+  </si>
+  <si>
     <t>Ratio_SD (ADVI/NUTS)</t>
   </si>
   <si>
     <t>Subestimacion_Incertidumbre_Pct</t>
   </si>
   <si>
+    <t>HDI_ADVI_Contiene_Media_NUTS</t>
+  </si>
+  <si>
+    <t>Modelo (c) Besag ICAR + No Estructurado (Mejor LOO)</t>
+  </si>
+  <si>
+    <t>Modelo (d) BYM2 (Prior Beta(0.5, 0.5))</t>
+  </si>
+  <si>
     <t>Intercepto Cantonal (alpha)</t>
   </si>
   <si>
@@ -172,67 +182,145 @@
     <t>Elasticidad Área Territorial (beta_area)</t>
   </si>
   <si>
-    <t>Escala Espacial BYM2 (sigma_s)</t>
-  </si>
-  <si>
-    <t>Parámetro de Mezcla Espacial (rho)</t>
+    <t>Escala Espacial ICAR (sigma_phi)</t>
+  </si>
+  <si>
+    <t>Escala Efecto No Estructurado (sigma_theta)</t>
   </si>
   <si>
     <t>Dispersión Binomial Negativa (alpha_disp)</t>
   </si>
   <si>
-    <t>[1.5327, 1.7101]</t>
-  </si>
-  <si>
-    <t>[0.1995, 0.4422]</t>
-  </si>
-  <si>
-    <t>[0.0510, 0.1734]</t>
-  </si>
-  <si>
-    <t>[0.8449, 1.0320]</t>
-  </si>
-  <si>
-    <t>[0.0009, 0.1485]</t>
-  </si>
-  <si>
-    <t>[1.5588, 2.3266]</t>
-  </si>
-  <si>
-    <t>[1.2374, 1.4995]</t>
-  </si>
-  <si>
-    <t>[0.1903, 0.4278]</t>
-  </si>
-  <si>
-    <t>[0.0939, 0.3820]</t>
-  </si>
-  <si>
-    <t>[1.2423, 1.8463]</t>
-  </si>
-  <si>
-    <t>[0.5891, 0.9892]</t>
-  </si>
-  <si>
-    <t>[3.8136, 7.3525]</t>
-  </si>
-  <si>
-    <t>+32.6%</t>
-  </si>
-  <si>
-    <t>-1.7%</t>
-  </si>
-  <si>
-    <t>+57.8%</t>
-  </si>
-  <si>
-    <t>+69.7%</t>
-  </si>
-  <si>
-    <t>+59.2%</t>
-  </si>
-  <si>
-    <t>+79.0%</t>
+    <t>Escala Espacial Total BYM2 (sigma_s)</t>
+  </si>
+  <si>
+    <t>Parámetro de Mezcla Espacial Beta(0.5, 0.5) (rho)</t>
+  </si>
+  <si>
+    <t>[1.2811, 1.3805]</t>
+  </si>
+  <si>
+    <t>[0.2438, 0.3853]</t>
+  </si>
+  <si>
+    <t>[0.2788, 0.3617]</t>
+  </si>
+  <si>
+    <t>[2.4639, 2.6605]</t>
+  </si>
+  <si>
+    <t>[0.0036, 0.0607]</t>
+  </si>
+  <si>
+    <t>[5.5396, 9.1767]</t>
+  </si>
+  <si>
+    <t>[1.2817, 1.3812]</t>
+  </si>
+  <si>
+    <t>[0.2436, 0.3856]</t>
+  </si>
+  <si>
+    <t>[0.2788, 0.3613]</t>
+  </si>
+  <si>
+    <t>[2.1384, 2.3089]</t>
+  </si>
+  <si>
+    <t>[0.9991, 1.0000]</t>
+  </si>
+  <si>
+    <t>[5.5562, 9.1987]</t>
+  </si>
+  <si>
+    <t>[1.2433, 1.4991]</t>
+  </si>
+  <si>
+    <t>[0.1934, 0.4225]</t>
+  </si>
+  <si>
+    <t>[0.0959, 0.3861]</t>
+  </si>
+  <si>
+    <t>[1.1373, 2.0912]</t>
+  </si>
+  <si>
+    <t>[0.1196, 0.8542]</t>
+  </si>
+  <si>
+    <t>[3.7865, 7.2327]</t>
+  </si>
+  <si>
+    <t>[1.2449, 1.4973]</t>
+  </si>
+  <si>
+    <t>[0.1926, 0.4336]</t>
+  </si>
+  <si>
+    <t>[0.0918, 0.3782]</t>
+  </si>
+  <si>
+    <t>[1.2232, 1.8205]</t>
+  </si>
+  <si>
+    <t>[0.5762, 0.9932]</t>
+  </si>
+  <si>
+    <t>[3.8222, 7.2670]</t>
+  </si>
+  <si>
+    <t>+61.4%</t>
+  </si>
+  <si>
+    <t>+38.0%</t>
+  </si>
+  <si>
+    <t>+70.9%</t>
+  </si>
+  <si>
+    <t>+79.8%</t>
+  </si>
+  <si>
+    <t>+90.8%</t>
+  </si>
+  <si>
+    <t>-3.4%</t>
+  </si>
+  <si>
+    <t>+61.3%</t>
+  </si>
+  <si>
+    <t>+41.1%</t>
+  </si>
+  <si>
+    <t>+72.5%</t>
+  </si>
+  <si>
+    <t>+99.3%</t>
+  </si>
+  <si>
+    <t>-0.8%</t>
+  </si>
+  <si>
+    <t>SÍ</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Pearson_r</t>
+  </si>
+  <si>
+    <t>Pearson_p_valor</t>
+  </si>
+  <si>
+    <t>Spearman_rho</t>
+  </si>
+  <si>
+    <t>Spearman_p_valor</t>
+  </si>
+  <si>
+    <t>N_Subcircuitos</t>
   </si>
   <si>
     <t>Semilla</t>
@@ -241,10 +329,10 @@
     <t>ELBO_Final</t>
   </si>
   <si>
-    <t>ELBO_Meseta_Media</t>
-  </si>
-  <si>
-    <t>Iteraciones</t>
+    <t>Variacion_ELBO_Ultimas_5k_Pct</t>
+  </si>
+  <si>
+    <t>Criterio_Convergencia</t>
   </si>
   <si>
     <t>Convergio</t>
@@ -268,22 +356,16 @@
     <t>beta_area_sd</t>
   </si>
   <si>
-    <t>sigma_s_media</t>
-  </si>
-  <si>
-    <t>sigma_s_sd</t>
-  </si>
-  <si>
-    <t>rho_media</t>
-  </si>
-  <si>
-    <t>rho_sd</t>
-  </si>
-  <si>
-    <t>rho_hdi_inf</t>
-  </si>
-  <si>
-    <t>rho_hdi_sup</t>
+    <t>sigma_phi_media</t>
+  </si>
+  <si>
+    <t>sigma_phi_sd</t>
+  </si>
+  <si>
+    <t>sigma_theta_media</t>
+  </si>
+  <si>
+    <t>sigma_theta_sd</t>
   </si>
   <si>
     <t>alpha_disp_media</t>
@@ -298,10 +380,16 @@
     <t>Desv. Est. (Entre Semillas)</t>
   </si>
   <si>
-    <t>Sí (100%)</t>
+    <t>Var 5k &lt; 0.1%</t>
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Sí (3/3)</t>
   </si>
 </sst>
 </file>
@@ -659,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -696,28 +784,28 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>1.6235</v>
+        <v>1.3482</v>
       </c>
       <c r="C2">
-        <v>0.0449</v>
+        <v>0.0249</v>
       </c>
       <c r="D2">
-        <v>1.54</v>
+        <v>1.3009</v>
       </c>
       <c r="E2">
-        <v>1.7101</v>
+        <v>1.395</v>
       </c>
       <c r="F2">
-        <v>0.001</v>
+        <v>0.0005</v>
       </c>
       <c r="G2">
-        <v>0.0007</v>
+        <v>0.0004</v>
       </c>
       <c r="H2">
-        <v>1919.8995</v>
+        <v>2083.4064</v>
       </c>
       <c r="I2">
-        <v>1779.1585</v>
+        <v>1940.7928</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -725,28 +813,28 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.3175</v>
+        <v>0.3207</v>
       </c>
       <c r="C3">
-        <v>0.0613</v>
+        <v>0.036</v>
       </c>
       <c r="D3">
-        <v>0.2047</v>
+        <v>0.2522</v>
       </c>
       <c r="E3">
-        <v>0.4369</v>
+        <v>0.3853</v>
       </c>
       <c r="F3">
-        <v>0.0013</v>
+        <v>0.0008</v>
       </c>
       <c r="G3">
-        <v>0.001</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H3">
-        <v>2114.2896</v>
+        <v>2130.9263</v>
       </c>
       <c r="I3">
-        <v>1782.2167</v>
+        <v>1885.5594</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -754,28 +842,28 @@
         <v>11</v>
       </c>
       <c r="B4">
-        <v>0.114</v>
+        <v>0.3242</v>
       </c>
       <c r="C4">
-        <v>0.0316</v>
+        <v>0.0196</v>
       </c>
       <c r="D4">
-        <v>0.0541</v>
+        <v>0.2873</v>
       </c>
       <c r="E4">
-        <v>0.1725</v>
+        <v>0.3595</v>
       </c>
       <c r="F4">
-        <v>0.0007</v>
+        <v>0.0005</v>
       </c>
       <c r="G4">
-        <v>0.0005</v>
+        <v>0.0003</v>
       </c>
       <c r="H4">
-        <v>1893.0735</v>
+        <v>1812.8782</v>
       </c>
       <c r="I4">
-        <v>1920.3398</v>
+        <v>1849.0071</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -783,28 +871,28 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>0.9327</v>
+        <v>2.5948</v>
       </c>
       <c r="C5">
-        <v>0.047</v>
+        <v>0.0523</v>
       </c>
       <c r="D5">
-        <v>0.848</v>
+        <v>2.5028</v>
       </c>
       <c r="E5">
-        <v>1.0252</v>
+        <v>2.6991</v>
       </c>
       <c r="F5">
         <v>0.0011</v>
       </c>
       <c r="G5">
-        <v>0.0008</v>
+        <v>0.0009</v>
       </c>
       <c r="H5">
-        <v>1926.7957</v>
+        <v>2058.6563</v>
       </c>
       <c r="I5">
-        <v>1744.0399</v>
+        <v>1893.8092</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -812,57 +900,28 @@
         <v>13</v>
       </c>
       <c r="B6">
-        <v>0.0274</v>
+        <v>6.9813</v>
       </c>
       <c r="C6">
-        <v>0.0429</v>
+        <v>0.8841</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>5.3763</v>
       </c>
       <c r="E6">
-        <v>0.0906</v>
+        <v>8.5389</v>
       </c>
       <c r="F6">
-        <v>0.001</v>
+        <v>0.0205</v>
       </c>
       <c r="G6">
-        <v>0.0024</v>
+        <v>0.0143</v>
       </c>
       <c r="H6">
-        <v>1986.8933</v>
+        <v>1862.7627</v>
       </c>
       <c r="I6">
-        <v>1921.861</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7">
-        <v>1.8953</v>
-      </c>
-      <c r="C7">
-        <v>0.1903</v>
-      </c>
-      <c r="D7">
-        <v>1.5532</v>
-      </c>
-      <c r="E7">
-        <v>2.2696</v>
-      </c>
-      <c r="F7">
-        <v>0.0044</v>
-      </c>
-      <c r="G7">
-        <v>0.003</v>
-      </c>
-      <c r="H7">
-        <v>1862.6901</v>
-      </c>
-      <c r="I7">
-        <v>1882.1067</v>
+        <v>1922.7755</v>
       </c>
     </row>
   </sheetData>
@@ -872,167 +931,151 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>2000</v>
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5">
-        <v>-1473.724258527367</v>
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>26.17493962971699</v>
+        <v>-1219.559352321657</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>167.9849583339543</v>
+        <v>25.82227081422354</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>-1537.056294417802</v>
+        <v>103.4699346118752</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>30.86485530288633</v>
+        <v>-1233.7458212532</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>231.316994224389</v>
+        <v>26.7589567450958</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>242</v>
+        <v>117.6564035434187</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13">
-        <v>146</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+      <c r="B14">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15">
-        <v>0.02743806563775158</v>
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16">
-        <v>0.0009044670208433613</v>
+        <v>0.3207415208061377</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17">
-        <v>0.1484819000085819</v>
+        <v>0.2521431114241862</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18">
-        <v>0.3174807836015135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19">
-        <v>0.199521462273394</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20">
-        <v>0.4421612885874928</v>
+        <v>0.3922481193284321</v>
       </c>
     </row>
   </sheetData>
@@ -1042,210 +1085,501 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="L1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2">
-        <v>1.6235</v>
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
       </c>
       <c r="C2">
-        <v>0.0449</v>
-      </c>
-      <c r="D2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2">
-        <v>1.3701</v>
+        <v>1.332</v>
+      </c>
+      <c r="D2">
+        <v>0.0252</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
       </c>
       <c r="F2">
-        <v>0.0667</v>
-      </c>
-      <c r="G2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2">
-        <v>0.6737</v>
-      </c>
-      <c r="I2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>1.3703</v>
+      </c>
+      <c r="G2">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2">
+        <v>-2.79</v>
+      </c>
+      <c r="J2">
+        <v>0.3863</v>
+      </c>
+      <c r="K2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>49</v>
       </c>
-      <c r="B3">
-        <v>0.3175</v>
+      <c r="B3" t="s">
+        <v>52</v>
       </c>
       <c r="C3">
-        <v>0.0613</v>
-      </c>
-      <c r="D3" t="s">
+        <v>0.3126</v>
+      </c>
+      <c r="D3">
+        <v>0.0357</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3">
+        <v>0.3101</v>
+      </c>
+      <c r="G3">
+        <v>0.0577</v>
+      </c>
+      <c r="H3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3">
+        <v>0.79</v>
+      </c>
+      <c r="J3">
+        <v>0.62</v>
+      </c>
+      <c r="K3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4">
+        <v>0.3215</v>
+      </c>
+      <c r="D4">
+        <v>0.0214</v>
+      </c>
+      <c r="E4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4">
+        <v>0.2322</v>
+      </c>
+      <c r="G4">
+        <v>0.0737</v>
+      </c>
+      <c r="H4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4">
+        <v>38.45</v>
+      </c>
+      <c r="J4">
+        <v>0.2906</v>
+      </c>
+      <c r="K4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5">
+        <v>2.5583</v>
+      </c>
+      <c r="D5">
+        <v>0.0494</v>
+      </c>
+      <c r="E5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5">
+        <v>1.5868</v>
+      </c>
+      <c r="G5">
+        <v>0.244</v>
+      </c>
+      <c r="H5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5">
+        <v>61.22</v>
+      </c>
+      <c r="J5">
+        <v>0.2025</v>
+      </c>
+      <c r="K5" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
         <v>55</v>
       </c>
-      <c r="E3">
-        <v>0.3093</v>
-      </c>
-      <c r="F3">
-        <v>0.0603</v>
-      </c>
-      <c r="G3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3">
-        <v>1.0172</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="C6">
+        <v>0.0192</v>
+      </c>
+      <c r="D6">
+        <v>0.0155</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6">
+        <v>0.5803</v>
+      </c>
+      <c r="G6">
+        <v>0.1688</v>
+      </c>
+      <c r="H6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6">
+        <v>-96.69</v>
+      </c>
+      <c r="J6">
+        <v>0.0917</v>
+      </c>
+      <c r="K6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7">
+        <v>7.0989</v>
+      </c>
+      <c r="D7">
+        <v>0.8997000000000001</v>
+      </c>
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7">
+        <v>5.3233</v>
+      </c>
+      <c r="G7">
+        <v>0.8704</v>
+      </c>
+      <c r="H7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7">
+        <v>33.35</v>
+      </c>
+      <c r="J7">
+        <v>1.0337</v>
+      </c>
+      <c r="K7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8">
+        <v>1.3327</v>
+      </c>
+      <c r="D8">
+        <v>0.0252</v>
+      </c>
+      <c r="E8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8">
+        <v>1.3702</v>
+      </c>
+      <c r="G8">
+        <v>0.065</v>
+      </c>
+      <c r="H8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8">
+        <v>-2.74</v>
+      </c>
+      <c r="J8">
+        <v>0.387</v>
+      </c>
+      <c r="K8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9">
+        <v>0.3126</v>
+      </c>
+      <c r="D9">
+        <v>0.0359</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9">
+        <v>0.3112</v>
+      </c>
+      <c r="G9">
+        <v>0.0609</v>
+      </c>
+      <c r="H9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9">
+        <v>0.45</v>
+      </c>
+      <c r="J9">
+        <v>0.5891999999999999</v>
+      </c>
+      <c r="K9" t="s">
+        <v>90</v>
+      </c>
+      <c r="L9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10">
+        <v>0.3212</v>
+      </c>
+      <c r="D10">
+        <v>0.0213</v>
+      </c>
+      <c r="E10" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+      <c r="F10">
+        <v>0.2299</v>
+      </c>
+      <c r="G10">
+        <v>0.0733</v>
+      </c>
+      <c r="H10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10">
+        <v>39.73</v>
+      </c>
+      <c r="J10">
+        <v>0.2908</v>
+      </c>
+      <c r="K10" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
         <v>50</v>
       </c>
-      <c r="B4">
-        <v>0.114</v>
-      </c>
-      <c r="C4">
-        <v>0.0316</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11">
+        <v>2.2203</v>
+      </c>
+      <c r="D11">
+        <v>0.0429</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11">
+        <v>1.4992</v>
+      </c>
+      <c r="G11">
+        <v>0.1559</v>
+      </c>
+      <c r="H11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11">
+        <v>48.1</v>
+      </c>
+      <c r="J11">
+        <v>0.2749</v>
+      </c>
+      <c r="K11" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12">
+        <v>0.9998</v>
+      </c>
+      <c r="D12">
+        <v>0.0007</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12">
+        <v>0.8199</v>
+      </c>
+      <c r="G12">
+        <v>0.1055</v>
+      </c>
+      <c r="H12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12">
+        <v>21.94</v>
+      </c>
+      <c r="J12">
+        <v>0.0069</v>
+      </c>
+      <c r="K12" t="s">
+        <v>92</v>
+      </c>
+      <c r="L12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
         <v>56</v>
       </c>
-      <c r="E4">
-        <v>0.2306</v>
-      </c>
-      <c r="F4">
-        <v>0.075</v>
-      </c>
-      <c r="G4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4">
-        <v>0.422</v>
-      </c>
-      <c r="I4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5">
-        <v>0.9327</v>
-      </c>
-      <c r="C5">
-        <v>0.047</v>
-      </c>
-      <c r="D5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5">
-        <v>1.4986</v>
-      </c>
-      <c r="F5">
-        <v>0.1553</v>
-      </c>
-      <c r="G5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5">
-        <v>0.3025</v>
-      </c>
-      <c r="I5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6">
-        <v>0.0274</v>
-      </c>
-      <c r="C6">
-        <v>0.0429</v>
-      </c>
-      <c r="D6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6">
-        <v>0.8127</v>
-      </c>
-      <c r="F6">
-        <v>0.1052</v>
-      </c>
-      <c r="G6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6">
-        <v>0.4078</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="C13">
+        <v>7.118</v>
+      </c>
+      <c r="D13">
+        <v>0.9011</v>
+      </c>
+      <c r="E13" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7">
-        <v>1.8953</v>
-      </c>
-      <c r="C7">
-        <v>0.1903</v>
-      </c>
-      <c r="D7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7">
-        <v>5.3588</v>
-      </c>
-      <c r="F7">
-        <v>0.9064</v>
-      </c>
-      <c r="G7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H7">
-        <v>0.2099</v>
-      </c>
-      <c r="I7" t="s">
-        <v>71</v>
+      <c r="F13">
+        <v>5.3177</v>
+      </c>
+      <c r="G13">
+        <v>0.8944</v>
+      </c>
+      <c r="H13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13">
+        <v>33.85</v>
+      </c>
+      <c r="J13">
+        <v>1.0075</v>
+      </c>
+      <c r="K13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1255,361 +1589,395 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2">
+        <v>0.9952</v>
+      </c>
+      <c r="C2">
+        <v>1.34E-246</v>
+      </c>
+      <c r="D2">
+        <v>0.996</v>
+      </c>
+      <c r="E2">
+        <v>3.07E-256</v>
+      </c>
+      <c r="F2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3">
+        <v>0.9949</v>
+      </c>
+      <c r="C3">
+        <v>4.85E-243</v>
+      </c>
+      <c r="D3">
+        <v>0.9959</v>
+      </c>
+      <c r="E3">
+        <v>8.92E-255</v>
+      </c>
+      <c r="F3">
+        <v>244</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>42</v>
       </c>
       <c r="B2">
-        <v>-3359.57</v>
+        <v>-1480.21</v>
       </c>
       <c r="C2">
-        <v>-1802.64</v>
-      </c>
-      <c r="D2">
-        <v>40000</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
+        <v>0.0076</v>
+      </c>
+      <c r="D2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="s">
+        <v>122</v>
       </c>
       <c r="F2">
-        <v>1.623524116197549</v>
+        <v>1.332005694650479</v>
       </c>
       <c r="G2">
-        <v>0.04491802682084656</v>
+        <v>0.02516312780517108</v>
       </c>
       <c r="H2">
-        <v>0.3174807836015135</v>
+        <v>0.3125963688782021</v>
       </c>
       <c r="I2">
-        <v>0.06132663748723281</v>
+        <v>0.03574931768889927</v>
       </c>
       <c r="J2">
-        <v>0.1139655428802458</v>
+        <v>0.3214628363099949</v>
       </c>
       <c r="K2">
-        <v>0.03163176786816241</v>
+        <v>0.02141195909625017</v>
       </c>
       <c r="L2">
-        <v>0.9326691078819246</v>
+        <v>2.558342875251677</v>
       </c>
       <c r="M2">
-        <v>0.04699295345166132</v>
+        <v>0.04939655817856773</v>
       </c>
       <c r="N2">
-        <v>0.02743806563775158</v>
+        <v>0.01922899493146631</v>
       </c>
       <c r="O2">
-        <v>0.04290666347412147</v>
+        <v>0.01548166862814764</v>
       </c>
       <c r="P2">
-        <v>0.0009044670208433613</v>
+        <v>7.098867776710443</v>
       </c>
       <c r="Q2">
-        <v>0.1484819000085819</v>
-      </c>
-      <c r="R2">
-        <v>1.895346243636717</v>
-      </c>
-      <c r="S2">
-        <v>0.1902601476808199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>0.8997399849432262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>123</v>
       </c>
       <c r="B3">
-        <v>-2487.22</v>
+        <v>-1410.77</v>
       </c>
       <c r="C3">
-        <v>-1770.63</v>
-      </c>
-      <c r="D3">
-        <v>40000</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
+        <v>0.0638</v>
+      </c>
+      <c r="D3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
       </c>
       <c r="F3">
-        <v>1.623778128408778</v>
+        <v>1.351918969314986</v>
       </c>
       <c r="G3">
-        <v>0.04584008542277374</v>
+        <v>0.02518978102619612</v>
       </c>
       <c r="H3">
-        <v>0.3157588275025591</v>
+        <v>0.319605347837042</v>
       </c>
       <c r="I3">
-        <v>0.06362749840830575</v>
+        <v>0.03630999987746104</v>
       </c>
       <c r="J3">
-        <v>0.1174209625611862</v>
+        <v>0.3161343921845154</v>
       </c>
       <c r="K3">
-        <v>0.03042671778153327</v>
+        <v>0.02059773163886027</v>
       </c>
       <c r="L3">
-        <v>0.9409101874383361</v>
+        <v>2.605343004977112</v>
       </c>
       <c r="M3">
-        <v>0.046780919908641</v>
+        <v>0.05651159955244913</v>
       </c>
       <c r="N3">
-        <v>0.02709636327193479</v>
+        <v>0.02047420476246393</v>
       </c>
       <c r="O3">
-        <v>0.04744799163816882</v>
+        <v>0.0175495252095893</v>
       </c>
       <c r="P3">
-        <v>0.0009279205806517582</v>
+        <v>7.204266652214683</v>
       </c>
       <c r="Q3">
-        <v>0.145583162857086</v>
-      </c>
-      <c r="R3">
-        <v>1.885934853597718</v>
-      </c>
-      <c r="S3">
-        <v>0.1876216406785289</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
+        <v>0.9431206763929584</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>999</v>
       </c>
       <c r="B4">
-        <v>-1643.06</v>
+        <v>-1427.04</v>
       </c>
       <c r="C4">
-        <v>-1816.74</v>
-      </c>
-      <c r="D4">
-        <v>40000</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
+        <v>0.0578</v>
+      </c>
+      <c r="D4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" t="s">
+        <v>122</v>
       </c>
       <c r="F4">
-        <v>1.628772147178876</v>
+        <v>1.332831010468481</v>
       </c>
       <c r="G4">
-        <v>0.04522113317609407</v>
+        <v>0.02625027291831595</v>
       </c>
       <c r="H4">
-        <v>0.315314504040495</v>
+        <v>0.3112868222927571</v>
       </c>
       <c r="I4">
-        <v>0.05965156012589985</v>
+        <v>0.03383968101270034</v>
       </c>
       <c r="J4">
-        <v>0.1161786593041603</v>
+        <v>0.3255962606921124</v>
       </c>
       <c r="K4">
-        <v>0.03122912729683145</v>
+        <v>0.01962156322285576</v>
       </c>
       <c r="L4">
-        <v>0.9323345727414417</v>
+        <v>2.605821791190158</v>
       </c>
       <c r="M4">
-        <v>0.04684206540636381</v>
+        <v>0.05622828872385578</v>
       </c>
       <c r="N4">
-        <v>0.02661597530497388</v>
+        <v>0.01894117873855222</v>
       </c>
       <c r="O4">
-        <v>0.04251419240636662</v>
+        <v>0.01417912455200152</v>
       </c>
       <c r="P4">
-        <v>0.0008799909937939831</v>
+        <v>7.252540700545737</v>
       </c>
       <c r="Q4">
-        <v>0.1497816357182009</v>
-      </c>
-      <c r="R4">
-        <v>1.862355073398196</v>
-      </c>
-      <c r="S4">
-        <v>0.1884001193438192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
+        <v>0.9228097371502897</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="B5">
-        <v>-2496.6167</v>
+        <v>-1439.34</v>
       </c>
       <c r="C5">
-        <v>-1796.67</v>
-      </c>
-      <c r="D5">
-        <v>40000</v>
+        <v>0.0431</v>
+      </c>
+      <c r="D5" t="s">
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F5">
-        <v>1.6254</v>
+        <v>1.3389</v>
       </c>
       <c r="G5">
-        <v>0.0453</v>
+        <v>0.0255</v>
       </c>
       <c r="H5">
-        <v>0.3162</v>
+        <v>0.3145</v>
       </c>
       <c r="I5">
-        <v>0.0615</v>
+        <v>0.0353</v>
       </c>
       <c r="J5">
-        <v>0.1159</v>
+        <v>0.3211</v>
       </c>
       <c r="K5">
-        <v>0.0311</v>
+        <v>0.0205</v>
       </c>
       <c r="L5">
-        <v>0.9353</v>
+        <v>2.5898</v>
       </c>
       <c r="M5">
-        <v>0.0469</v>
+        <v>0.054</v>
       </c>
       <c r="N5">
-        <v>0.0271</v>
+        <v>0.0195</v>
       </c>
       <c r="O5">
-        <v>0.0443</v>
+        <v>0.0157</v>
       </c>
       <c r="P5">
+        <v>7.1852</v>
+      </c>
+      <c r="Q5">
+        <v>0.9219000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6">
+        <v>36.3173</v>
+      </c>
+      <c r="C6">
+        <v>0.0309</v>
+      </c>
+      <c r="D6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6">
+        <v>0.0113</v>
+      </c>
+      <c r="G6">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="H6">
+        <v>0.0045</v>
+      </c>
+      <c r="I6">
+        <v>0.0013</v>
+      </c>
+      <c r="J6">
+        <v>0.0047</v>
+      </c>
+      <c r="K6">
         <v>0.0009</v>
       </c>
-      <c r="Q5">
-        <v>0.1479</v>
-      </c>
-      <c r="R5">
-        <v>1.8812</v>
-      </c>
-      <c r="S5">
-        <v>0.1888</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6">
-        <v>858.2936</v>
-      </c>
-      <c r="C6">
-        <v>23.6276</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6">
-        <v>0.003</v>
-      </c>
-      <c r="G6">
-        <v>0.0005</v>
-      </c>
-      <c r="H6">
-        <v>0.0011</v>
-      </c>
-      <c r="I6">
-        <v>0.002</v>
-      </c>
-      <c r="J6">
-        <v>0.0018</v>
-      </c>
-      <c r="K6">
-        <v>0.0005999999999999999</v>
-      </c>
       <c r="L6">
-        <v>0.0049</v>
+        <v>0.0273</v>
       </c>
       <c r="M6">
-        <v>0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="N6">
-        <v>0.0004</v>
+        <v>0.0008</v>
       </c>
       <c r="O6">
-        <v>0.0027</v>
+        <v>0.0017</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>0.0786</v>
       </c>
       <c r="Q6">
-        <v>0.0021</v>
-      </c>
-      <c r="R6">
-        <v>0.017</v>
-      </c>
-      <c r="S6">
-        <v>0.0014</v>
+        <v>0.0217</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
+++ b/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="139">
   <si>
     <t>mean</t>
   </si>
@@ -119,7 +119,7 @@
     <t>Beta_Year HDI 95% Superior</t>
   </si>
   <si>
-    <t>Modelo (c) Binomial Negativa (ICAR + No Estructurado) [Mejor LOO-CV]</t>
+    <t>Modelo (b) Binomial Negativa (ICAR) [Mejor LOO-CV]</t>
   </si>
   <si>
     <t>ADVI (Automatic Differentiation Variational Inference, Adam lr=0.005)</t>
@@ -167,7 +167,10 @@
     <t>HDI_ADVI_Contiene_Media_NUTS</t>
   </si>
   <si>
-    <t>Modelo (c) Besag ICAR + No Estructurado (Mejor LOO)</t>
+    <t>Modelo (b) Binomial Negativa (ICAR) [Mejor LOO]</t>
+  </si>
+  <si>
+    <t>Modelo (c) Besag ICAR + No Estructurado</t>
   </si>
   <si>
     <t>Modelo (d) BYM2 (Prior Beta(0.5, 0.5))</t>
@@ -185,18 +188,33 @@
     <t>Escala Espacial ICAR (sigma_phi)</t>
   </si>
   <si>
+    <t>Dispersión Binomial Negativa (alpha_disp)</t>
+  </si>
+  <si>
     <t>Escala Efecto No Estructurado (sigma_theta)</t>
   </si>
   <si>
-    <t>Dispersión Binomial Negativa (alpha_disp)</t>
-  </si>
-  <si>
     <t>Escala Espacial Total BYM2 (sigma_s)</t>
   </si>
   <si>
     <t>Parámetro de Mezcla Espacial Beta(0.5, 0.5) (rho)</t>
   </si>
   <si>
+    <t>[1.2997, 1.3982]</t>
+  </si>
+  <si>
+    <t>[0.2521, 0.3922]</t>
+  </si>
+  <si>
+    <t>[0.2865, 0.3623]</t>
+  </si>
+  <si>
+    <t>[2.4965, 2.7038]</t>
+  </si>
+  <si>
+    <t>[5.4081, 8.7699]</t>
+  </si>
+  <si>
     <t>[1.2811, 1.3805]</t>
   </si>
   <si>
@@ -233,6 +251,21 @@
     <t>[5.5562, 9.1987]</t>
   </si>
   <si>
+    <t>[1.2696, 1.4681]</t>
+  </si>
+  <si>
+    <t>[0.1982, 0.4211]</t>
+  </si>
+  <si>
+    <t>[0.2034, 0.4555]</t>
+  </si>
+  <si>
+    <t>[1.8026, 2.3235]</t>
+  </si>
+  <si>
+    <t>[3.6346, 7.0755]</t>
+  </si>
+  <si>
     <t>[1.2433, 1.4991]</t>
   </si>
   <si>
@@ -269,6 +302,21 @@
     <t>[3.8222, 7.2670]</t>
   </si>
   <si>
+    <t>+50.9%</t>
+  </si>
+  <si>
+    <t>+38.2%</t>
+  </si>
+  <si>
+    <t>+69.5%</t>
+  </si>
+  <si>
+    <t>+61.0%</t>
+  </si>
+  <si>
+    <t>-1.0%</t>
+  </si>
+  <si>
     <t>+61.4%</t>
   </si>
   <si>
@@ -362,12 +410,6 @@
     <t>sigma_phi_sd</t>
   </si>
   <si>
-    <t>sigma_theta_media</t>
-  </si>
-  <si>
-    <t>sigma_theta_sd</t>
-  </si>
-  <si>
     <t>alpha_disp_media</t>
   </si>
   <si>
@@ -389,7 +431,10 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>Sí (3/3)</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Parcial</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1131,37 +1176,37 @@
         <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2">
-        <v>1.332</v>
+        <v>1.3482</v>
       </c>
       <c r="D2">
-        <v>0.0252</v>
+        <v>0.0249</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F2">
-        <v>1.3703</v>
+        <v>1.3682</v>
       </c>
       <c r="G2">
-        <v>0.06510000000000001</v>
+        <v>0.0507</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I2">
-        <v>-2.79</v>
+        <v>-1.46</v>
       </c>
       <c r="J2">
-        <v>0.3863</v>
+        <v>0.4907</v>
       </c>
       <c r="K2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="L2" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1169,37 +1214,37 @@
         <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3">
-        <v>0.3126</v>
+        <v>0.3207</v>
       </c>
       <c r="D3">
-        <v>0.0357</v>
+        <v>0.036</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F3">
-        <v>0.3101</v>
+        <v>0.3104</v>
       </c>
       <c r="G3">
-        <v>0.0577</v>
+        <v>0.0582</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I3">
-        <v>0.79</v>
+        <v>3.34</v>
       </c>
       <c r="J3">
-        <v>0.62</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1207,37 +1252,37 @@
         <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
-        <v>0.3215</v>
+        <v>0.3242</v>
       </c>
       <c r="D4">
-        <v>0.0214</v>
+        <v>0.0196</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4">
-        <v>0.2322</v>
+        <v>0.3223</v>
       </c>
       <c r="G4">
-        <v>0.0737</v>
+        <v>0.0641</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I4">
-        <v>38.45</v>
+        <v>0.6</v>
       </c>
       <c r="J4">
-        <v>0.2906</v>
+        <v>0.305</v>
       </c>
       <c r="K4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="L4" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1245,37 +1290,37 @@
         <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5">
-        <v>2.5583</v>
+        <v>2.5948</v>
       </c>
       <c r="D5">
-        <v>0.0494</v>
+        <v>0.0523</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5">
-        <v>1.5868</v>
+        <v>2.0494</v>
       </c>
       <c r="G5">
-        <v>0.244</v>
+        <v>0.1342</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I5">
-        <v>61.22</v>
+        <v>26.61</v>
       </c>
       <c r="J5">
-        <v>0.2025</v>
+        <v>0.3896</v>
       </c>
       <c r="K5" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L5" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1283,75 +1328,75 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>0.0192</v>
+        <v>6.9813</v>
       </c>
       <c r="D6">
-        <v>0.0155</v>
+        <v>0.8838</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6">
-        <v>0.5803</v>
+        <v>5.1165</v>
       </c>
       <c r="G6">
-        <v>0.1688</v>
+        <v>0.8751</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I6">
-        <v>-96.69</v>
+        <v>36.45</v>
       </c>
       <c r="J6">
-        <v>0.0917</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="L6" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C7">
-        <v>7.0989</v>
+        <v>1.332</v>
       </c>
       <c r="D7">
-        <v>0.8997000000000001</v>
+        <v>0.0252</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F7">
-        <v>5.3233</v>
+        <v>1.3703</v>
       </c>
       <c r="G7">
-        <v>0.8704</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I7">
-        <v>33.35</v>
+        <v>-2.79</v>
       </c>
       <c r="J7">
-        <v>1.0337</v>
+        <v>0.3863</v>
       </c>
       <c r="K7" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="L7" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1359,37 +1404,37 @@
         <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8">
-        <v>1.3327</v>
+        <v>0.3126</v>
       </c>
       <c r="D8">
-        <v>0.0252</v>
+        <v>0.0357</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F8">
-        <v>1.3702</v>
+        <v>0.3101</v>
       </c>
       <c r="G8">
-        <v>0.065</v>
+        <v>0.0577</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I8">
-        <v>-2.74</v>
+        <v>0.79</v>
       </c>
       <c r="J8">
-        <v>0.387</v>
+        <v>0.62</v>
       </c>
       <c r="K8" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="L8" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1397,37 +1442,37 @@
         <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9">
-        <v>0.3126</v>
+        <v>0.3215</v>
       </c>
       <c r="D9">
-        <v>0.0359</v>
+        <v>0.0214</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9">
-        <v>0.3112</v>
+        <v>0.2322</v>
       </c>
       <c r="G9">
-        <v>0.0609</v>
+        <v>0.0737</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I9">
-        <v>0.45</v>
+        <v>38.45</v>
       </c>
       <c r="J9">
-        <v>0.5891999999999999</v>
+        <v>0.2906</v>
       </c>
       <c r="K9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="L9" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1435,37 +1480,37 @@
         <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C10">
-        <v>0.3212</v>
+        <v>2.5583</v>
       </c>
       <c r="D10">
-        <v>0.0213</v>
+        <v>0.0494</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10">
-        <v>0.2299</v>
+        <v>1.5868</v>
       </c>
       <c r="G10">
-        <v>0.0733</v>
+        <v>0.244</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I10">
-        <v>39.73</v>
+        <v>61.22</v>
       </c>
       <c r="J10">
-        <v>0.2908</v>
+        <v>0.2025</v>
       </c>
       <c r="K10" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L10" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1476,34 +1521,34 @@
         <v>57</v>
       </c>
       <c r="C11">
-        <v>2.2203</v>
+        <v>0.0192</v>
       </c>
       <c r="D11">
-        <v>0.0429</v>
+        <v>0.0155</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11">
-        <v>1.4992</v>
+        <v>0.5803</v>
       </c>
       <c r="G11">
-        <v>0.1559</v>
+        <v>0.1688</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="I11">
-        <v>48.1</v>
+        <v>-96.69</v>
       </c>
       <c r="J11">
-        <v>0.2749</v>
+        <v>0.0917</v>
       </c>
       <c r="K11" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="L11" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1511,75 +1556,265 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C12">
-        <v>0.9998</v>
+        <v>7.0989</v>
       </c>
       <c r="D12">
-        <v>0.0007</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F12">
-        <v>0.8199</v>
+        <v>5.3233</v>
       </c>
       <c r="G12">
-        <v>0.1055</v>
+        <v>0.8704</v>
       </c>
       <c r="H12" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I12">
-        <v>21.94</v>
+        <v>33.35</v>
       </c>
       <c r="J12">
-        <v>0.0069</v>
+        <v>1.0337</v>
       </c>
       <c r="K12" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13">
+        <v>1.3327</v>
+      </c>
+      <c r="D13">
+        <v>0.0252</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13">
+        <v>1.3702</v>
+      </c>
+      <c r="G13">
+        <v>0.065</v>
+      </c>
+      <c r="H13" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13">
+        <v>-2.74</v>
+      </c>
+      <c r="J13">
+        <v>0.387</v>
+      </c>
+      <c r="K13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14">
+        <v>0.3126</v>
+      </c>
+      <c r="D14">
+        <v>0.0359</v>
+      </c>
+      <c r="E14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14">
+        <v>0.3112</v>
+      </c>
+      <c r="G14">
+        <v>0.0609</v>
+      </c>
+      <c r="H14" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14">
+        <v>0.45</v>
+      </c>
+      <c r="J14">
+        <v>0.5891999999999999</v>
+      </c>
+      <c r="K14" t="s">
+        <v>106</v>
+      </c>
+      <c r="L14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15">
+        <v>0.3212</v>
+      </c>
+      <c r="D15">
+        <v>0.0213</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15">
+        <v>0.2299</v>
+      </c>
+      <c r="G15">
+        <v>0.0733</v>
+      </c>
+      <c r="H15" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15">
+        <v>39.73</v>
+      </c>
+      <c r="J15">
+        <v>0.2908</v>
+      </c>
+      <c r="K15" t="s">
+        <v>101</v>
+      </c>
+      <c r="L15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16">
+        <v>2.2203</v>
+      </c>
+      <c r="D16">
+        <v>0.0429</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16">
+        <v>1.4992</v>
+      </c>
+      <c r="G16">
+        <v>0.1559</v>
+      </c>
+      <c r="H16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16">
+        <v>48.1</v>
+      </c>
+      <c r="J16">
+        <v>0.2749</v>
+      </c>
+      <c r="K16" t="s">
+        <v>107</v>
+      </c>
+      <c r="L16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17">
+        <v>0.9998</v>
+      </c>
+      <c r="D17">
+        <v>0.0007</v>
+      </c>
+      <c r="E17" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17">
+        <v>0.8199</v>
+      </c>
+      <c r="G17">
+        <v>0.1055</v>
+      </c>
+      <c r="H17" t="s">
+        <v>92</v>
+      </c>
+      <c r="I17">
+        <v>21.94</v>
+      </c>
+      <c r="J17">
+        <v>0.0069</v>
+      </c>
+      <c r="K17" t="s">
+        <v>108</v>
+      </c>
+      <c r="L17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
         <v>56</v>
       </c>
-      <c r="C13">
+      <c r="C18">
         <v>7.118</v>
       </c>
-      <c r="D13">
+      <c r="D18">
         <v>0.9011</v>
       </c>
-      <c r="E13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13">
+      <c r="E18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18">
         <v>5.3177</v>
       </c>
-      <c r="G13">
+      <c r="G18">
         <v>0.8944</v>
       </c>
-      <c r="H13" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13">
+      <c r="H18" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18">
         <v>33.85</v>
       </c>
-      <c r="J13">
+      <c r="J18">
         <v>1.0075</v>
       </c>
-      <c r="K13" t="s">
-        <v>93</v>
-      </c>
-      <c r="L13" t="s">
-        <v>95</v>
+      <c r="K18" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1589,7 +1824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1597,19 +1832,19 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1617,16 +1852,16 @@
         <v>49</v>
       </c>
       <c r="B2">
-        <v>0.9952</v>
+        <v>0.9976</v>
       </c>
       <c r="C2">
-        <v>1.34E-246</v>
+        <v>1.9E-283</v>
       </c>
       <c r="D2">
-        <v>0.996</v>
+        <v>0.9981</v>
       </c>
       <c r="E2">
-        <v>3.07E-256</v>
+        <v>6.65E-296</v>
       </c>
       <c r="F2">
         <v>244</v>
@@ -1637,18 +1872,38 @@
         <v>50</v>
       </c>
       <c r="B3">
+        <v>0.9952</v>
+      </c>
+      <c r="C3">
+        <v>1.34E-246</v>
+      </c>
+      <c r="D3">
+        <v>0.996</v>
+      </c>
+      <c r="E3">
+        <v>3.07E-256</v>
+      </c>
+      <c r="F3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4">
         <v>0.9949</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>4.85E-243</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>0.9959</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>8.92E-255</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>244</v>
       </c>
     </row>
@@ -1659,325 +1914,289 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>42</v>
       </c>
       <c r="B2">
-        <v>-1480.21</v>
+        <v>-1463.57</v>
       </c>
       <c r="C2">
-        <v>0.0076</v>
+        <v>0.0239</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="F2">
-        <v>1.332005694650479</v>
+        <v>1.348215695543547</v>
       </c>
       <c r="G2">
-        <v>0.02516312780517108</v>
+        <v>0.02486440077844795</v>
       </c>
       <c r="H2">
-        <v>0.3125963688782021</v>
+        <v>0.3207415208061377</v>
       </c>
       <c r="I2">
-        <v>0.03574931768889927</v>
+        <v>0.03599026148128612</v>
       </c>
       <c r="J2">
-        <v>0.3214628363099949</v>
+        <v>0.3242401336987106</v>
       </c>
       <c r="K2">
-        <v>0.02141195909625017</v>
+        <v>0.01956712105023788</v>
       </c>
       <c r="L2">
-        <v>2.558342875251677</v>
+        <v>2.594779781848443</v>
       </c>
       <c r="M2">
-        <v>0.04939655817856773</v>
+        <v>0.05228587069472689</v>
       </c>
       <c r="N2">
-        <v>0.01922899493146631</v>
+        <v>6.981329354578524</v>
       </c>
       <c r="O2">
-        <v>0.01548166862814764</v>
-      </c>
-      <c r="P2">
-        <v>7.098867776710443</v>
-      </c>
-      <c r="Q2">
-        <v>0.8997399849432262</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
+        <v>0.8838439947764355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>123</v>
       </c>
       <c r="B3">
-        <v>-1410.77</v>
+        <v>-1403.44</v>
       </c>
       <c r="C3">
-        <v>0.0638</v>
+        <v>0.2038</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F3">
-        <v>1.351918969314986</v>
+        <v>1.345572138536676</v>
       </c>
       <c r="G3">
-        <v>0.02518978102619612</v>
+        <v>0.02644417649281535</v>
       </c>
       <c r="H3">
-        <v>0.319605347837042</v>
+        <v>0.3131006868787864</v>
       </c>
       <c r="I3">
-        <v>0.03630999987746104</v>
+        <v>0.03444523211483167</v>
       </c>
       <c r="J3">
-        <v>0.3161343921845154</v>
+        <v>0.3260877571401382</v>
       </c>
       <c r="K3">
-        <v>0.02059773163886027</v>
+        <v>0.01917872834715813</v>
       </c>
       <c r="L3">
-        <v>2.605343004977112</v>
+        <v>2.611742165145061</v>
       </c>
       <c r="M3">
-        <v>0.05651159955244913</v>
+        <v>0.05259287166703557</v>
       </c>
       <c r="N3">
-        <v>0.02047420476246393</v>
+        <v>7.553946328661643</v>
       </c>
       <c r="O3">
-        <v>0.0175495252095893</v>
-      </c>
-      <c r="P3">
-        <v>7.204266652214683</v>
-      </c>
-      <c r="Q3">
-        <v>0.9431206763929584</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17">
+        <v>0.9755447672401087</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>999</v>
       </c>
       <c r="B4">
-        <v>-1427.04</v>
+        <v>-1566.81</v>
       </c>
       <c r="C4">
-        <v>0.0578</v>
+        <v>0.0541</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="F4">
-        <v>1.332831010468481</v>
+        <v>1.355457734654589</v>
       </c>
       <c r="G4">
-        <v>0.02625027291831595</v>
+        <v>0.02816734406081621</v>
       </c>
       <c r="H4">
-        <v>0.3112868222927571</v>
+        <v>0.328934224832281</v>
       </c>
       <c r="I4">
-        <v>0.03383968101270034</v>
+        <v>0.03761217287548037</v>
       </c>
       <c r="J4">
-        <v>0.3255962606921124</v>
+        <v>0.3314744399487521</v>
       </c>
       <c r="K4">
-        <v>0.01962156322285576</v>
+        <v>0.0204700482263286</v>
       </c>
       <c r="L4">
-        <v>2.605821791190158</v>
+        <v>2.630751287642934</v>
       </c>
       <c r="M4">
-        <v>0.05622828872385578</v>
+        <v>0.05140556772530547</v>
       </c>
       <c r="N4">
-        <v>0.01894117873855222</v>
+        <v>7.223352763380353</v>
       </c>
       <c r="O4">
-        <v>0.01417912455200152</v>
-      </c>
-      <c r="P4">
-        <v>7.252540700545737</v>
-      </c>
-      <c r="Q4">
-        <v>0.9228097371502897</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+        <v>0.9118138698189874</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B5">
-        <v>-1439.34</v>
+        <v>-1477.94</v>
       </c>
       <c r="C5">
-        <v>0.0431</v>
+        <v>0.0939</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F5">
-        <v>1.3389</v>
+        <v>1.3497</v>
       </c>
       <c r="G5">
-        <v>0.0255</v>
+        <v>0.0265</v>
       </c>
       <c r="H5">
-        <v>0.3145</v>
+        <v>0.3209</v>
       </c>
       <c r="I5">
-        <v>0.0353</v>
+        <v>0.036</v>
       </c>
       <c r="J5">
-        <v>0.3211</v>
+        <v>0.3273</v>
       </c>
       <c r="K5">
-        <v>0.0205</v>
+        <v>0.0197</v>
       </c>
       <c r="L5">
-        <v>2.5898</v>
+        <v>2.6124</v>
       </c>
       <c r="M5">
-        <v>0.054</v>
+        <v>0.0521</v>
       </c>
       <c r="N5">
-        <v>0.0195</v>
+        <v>7.2529</v>
       </c>
       <c r="O5">
-        <v>0.0157</v>
-      </c>
-      <c r="P5">
-        <v>7.1852</v>
-      </c>
-      <c r="Q5">
-        <v>0.9219000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17">
+        <v>0.9237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B6">
-        <v>36.3173</v>
+        <v>82.6275</v>
       </c>
       <c r="C6">
-        <v>0.0309</v>
+        <v>0.0963</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F6">
-        <v>0.0113</v>
+        <v>0.0051</v>
       </c>
       <c r="G6">
+        <v>0.0017</v>
+      </c>
+      <c r="H6">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="I6">
+        <v>0.0016</v>
+      </c>
+      <c r="J6">
+        <v>0.0038</v>
+      </c>
+      <c r="K6">
+        <v>0.0007</v>
+      </c>
+      <c r="L6">
+        <v>0.018</v>
+      </c>
+      <c r="M6">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="H6">
-        <v>0.0045</v>
-      </c>
-      <c r="I6">
-        <v>0.0013</v>
-      </c>
-      <c r="J6">
-        <v>0.0047</v>
-      </c>
-      <c r="K6">
-        <v>0.0009</v>
-      </c>
-      <c r="L6">
-        <v>0.0273</v>
-      </c>
-      <c r="M6">
-        <v>0.004</v>
-      </c>
       <c r="N6">
-        <v>0.0008</v>
+        <v>0.2874</v>
       </c>
       <c r="O6">
-        <v>0.0017</v>
-      </c>
-      <c r="P6">
-        <v>0.0786</v>
-      </c>
-      <c r="Q6">
-        <v>0.0217</v>
+        <v>0.047</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
+++ b/outputs/tables/tabla_diagnosticos_bayesianos.xlsx
@@ -1024,7 +1024,7 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>-1219.559352321657</v>
+        <v>-1219.559352321656</v>
       </c>
     </row>
     <row r="7" spans="1:2">
